--- a/1-运维服务目录/0102-组织级运维服务目录.xlsx
+++ b/1-运维服务目录/0102-组织级运维服务目录.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="120" windowWidth="22188" windowHeight="9575" tabRatio="954" activeTab="5"/>
+    <workbookView windowHeight="18180" tabRatio="954" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="服务目录" sheetId="8" r:id="rId1"/>
@@ -14,8 +14,7 @@
     <sheet name="基础软件运维服务 （040301）" sheetId="12" r:id="rId5"/>
     <sheet name="应用软件运维服务 （040303）" sheetId="13" r:id="rId6"/>
   </sheets>
-  <definedNames/>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -80,7 +79,6 @@
         <sz val="9"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -91,7 +89,6 @@
         <sz val="9"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>。</t>
@@ -188,7 +185,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -199,7 +195,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -211,7 +206,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -222,7 +216,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -234,7 +227,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -248,7 +240,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -259,7 +250,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -273,7 +263,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -284,7 +273,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -298,7 +286,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -309,7 +296,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -323,7 +309,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -334,7 +319,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -507,7 +491,7 @@
     <t>对故障进行定位并解决或提供相关技术支持，以保证客户业务正常运行</t>
   </si>
   <si>
-    <t>枣安低空智控一体化平台；蒙阴两山智慧城市综合管理平台；烟台田园综合体智慧农业管理系统；</t>
+    <t>SPS产品支持服务</t>
   </si>
   <si>
     <t>1、对业务数据进行维护、更新；</t>
@@ -549,21 +533,14 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -571,7 +548,6 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -579,7 +555,6 @@
       <sz val="24"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -587,32 +562,28 @@
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u val="single"/>
+      <u/>
       <sz val="11"/>
       <color theme="10"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u val="single"/>
+      <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -620,7 +591,6 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -629,7 +599,6 @@
       <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -638,7 +607,6 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -647,7 +615,6 @@
       <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -656,7 +623,6 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -665,7 +631,6 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -673,7 +638,6 @@
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -682,7 +646,6 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -691,7 +654,6 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -700,7 +662,6 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -708,7 +669,6 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -716,7 +676,6 @@
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -724,7 +683,6 @@
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -732,7 +690,6 @@
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -740,20 +697,30 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="34">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.49987"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -935,12 +902,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39998"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.49987"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -951,6 +912,93 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -966,6 +1014,7 @@
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -974,6 +1023,7 @@
       <bottom style="medium">
         <color theme="4"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -982,6 +1032,7 @@
       <bottom style="medium">
         <color theme="4" tint="0.49998"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -996,6 +1047,7 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1010,6 +1062,7 @@
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="double">
@@ -1024,6 +1077,7 @@
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -1032,6 +1086,7 @@
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -1042,558 +1097,207 @@
       <bottom style="double">
         <color theme="4"/>
       </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="118">
+  <cellStyleXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment/>
-      <protection/>
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" applyNumberFormat="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" applyNumberFormat="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="6" applyNumberFormat="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" applyNumberFormat="0" applyFont="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="11" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="11" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="13" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="27">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="49" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="70" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="70" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1" quotePrefix="1"/>
   </cellXfs>
-  <cellStyles count="104">
-    <cellStyle name="Normal" xfId="0"/>
-    <cellStyle name="Percent" xfId="15"/>
-    <cellStyle name="Currency" xfId="16"/>
-    <cellStyle name="Currency [0]" xfId="17"/>
-    <cellStyle name="Comma" xfId="18"/>
-    <cellStyle name="Comma [0]" xfId="19"/>
-    <cellStyle name="Percent" xfId="20"/>
-    <cellStyle name="Currency" xfId="21"/>
-    <cellStyle name="Currency [0]" xfId="22"/>
-    <cellStyle name="Comma" xfId="23"/>
-    <cellStyle name="Comma [0]" xfId="24"/>
-    <cellStyle name="Percent" xfId="25"/>
-    <cellStyle name="Currency" xfId="26"/>
-    <cellStyle name="Currency [0]" xfId="27"/>
-    <cellStyle name="Comma" xfId="28"/>
-    <cellStyle name="Comma [0]" xfId="29"/>
-    <cellStyle name="Percent" xfId="30"/>
-    <cellStyle name="Currency" xfId="31"/>
-    <cellStyle name="Currency [0]" xfId="32"/>
-    <cellStyle name="Comma" xfId="33"/>
-    <cellStyle name="Comma [0]" xfId="34"/>
-    <cellStyle name="Percent" xfId="35"/>
-    <cellStyle name="Currency" xfId="36"/>
-    <cellStyle name="Currency [0]" xfId="37"/>
-    <cellStyle name="Comma" xfId="38"/>
-    <cellStyle name="Comma [0]" xfId="39"/>
-    <cellStyle name="Percent" xfId="40"/>
-    <cellStyle name="Currency" xfId="41"/>
-    <cellStyle name="Currency [0]" xfId="42"/>
-    <cellStyle name="Comma" xfId="43"/>
-    <cellStyle name="Comma [0]" xfId="44"/>
-    <cellStyle name="Percent" xfId="45"/>
-    <cellStyle name="Currency" xfId="46"/>
-    <cellStyle name="Currency [0]" xfId="47"/>
-    <cellStyle name="Comma" xfId="48"/>
-    <cellStyle name="Comma [0]" xfId="49"/>
+  <cellStyles count="55">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal" xfId="49"/>
     <cellStyle name="Percent" xfId="50"/>
     <cellStyle name="Currency" xfId="51"/>
     <cellStyle name="Currency [0]" xfId="52"/>
     <cellStyle name="Comma" xfId="53"/>
     <cellStyle name="Comma [0]" xfId="54"/>
-    <cellStyle name="Percent" xfId="55"/>
-    <cellStyle name="Currency" xfId="56"/>
-    <cellStyle name="Currency [0]" xfId="57"/>
-    <cellStyle name="Comma" xfId="58"/>
-    <cellStyle name="Comma [0]" xfId="59"/>
-    <cellStyle name="Percent" xfId="60"/>
-    <cellStyle name="Currency" xfId="61"/>
-    <cellStyle name="Currency [0]" xfId="62"/>
-    <cellStyle name="Comma" xfId="63"/>
-    <cellStyle name="Comma [0]" xfId="64"/>
-    <cellStyle name="千位分隔" xfId="65"/>
-    <cellStyle name="货币" xfId="66"/>
-    <cellStyle name="百分比" xfId="67"/>
-    <cellStyle name="千位分隔[0]" xfId="68"/>
-    <cellStyle name="货币[0]" xfId="69"/>
-    <cellStyle name="超链接" xfId="70"/>
-    <cellStyle name="已访问的超链接" xfId="71"/>
-    <cellStyle name="注释" xfId="72"/>
-    <cellStyle name="警告文本" xfId="73"/>
-    <cellStyle name="标题" xfId="74"/>
-    <cellStyle name="解释性文本" xfId="75"/>
-    <cellStyle name="标题 1" xfId="76"/>
-    <cellStyle name="标题 2" xfId="77"/>
-    <cellStyle name="标题 3" xfId="78"/>
-    <cellStyle name="标题 4" xfId="79"/>
-    <cellStyle name="输入" xfId="80"/>
-    <cellStyle name="输出" xfId="81"/>
-    <cellStyle name="计算" xfId="82"/>
-    <cellStyle name="检查单元格" xfId="83"/>
-    <cellStyle name="链接单元格" xfId="84"/>
-    <cellStyle name="汇总" xfId="85"/>
-    <cellStyle name="好" xfId="86"/>
-    <cellStyle name="差" xfId="87"/>
-    <cellStyle name="适中" xfId="88"/>
-    <cellStyle name="强调文字颜色 1" xfId="89"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="90"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="91"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="92"/>
-    <cellStyle name="强调文字颜色 2" xfId="93"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="94"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="95"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="96"/>
-    <cellStyle name="强调文字颜色 3" xfId="97"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="98"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="99"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="100"/>
-    <cellStyle name="强调文字颜色 4" xfId="101"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="102"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="103"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="104"/>
-    <cellStyle name="强调文字颜色 5" xfId="105"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="106"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="107"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="108"/>
-    <cellStyle name="强调文字颜色 6" xfId="109"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="110"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="111"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="112"/>
-    <cellStyle name="Percent" xfId="113"/>
-    <cellStyle name="Currency" xfId="114"/>
-    <cellStyle name="Currency [0]" xfId="115"/>
-    <cellStyle name="Comma" xfId="116"/>
-    <cellStyle name="Comma [0]" xfId="117"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1888,8 +1592,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="6" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10.5" customWidth="1"/>
     <col min="2" max="2" width="15.75" customWidth="1"/>
@@ -1897,7 +1602,7 @@
     <col min="4" max="4" width="70.25" style="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="55.5" customHeight="1">
+    <row r="1" ht="55.5" customHeight="1" spans="1:4">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -1905,7 +1610,7 @@
       <c r="C1" s="17"/>
       <c r="D1" s="17"/>
     </row>
-    <row r="2" spans="1:4" ht="48.75" customHeight="1">
+    <row r="2" ht="48.75" customHeight="1" spans="1:4">
       <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
@@ -1919,7 +1624,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="43.5" customHeight="1">
+    <row r="3" ht="43.5" customHeight="1" spans="1:4">
       <c r="A3" s="20" t="s">
         <v>5</v>
       </c>
@@ -1933,7 +1638,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="43.5" customHeight="1">
+    <row r="4" ht="43.5" customHeight="1" spans="1:4">
       <c r="A4" s="20"/>
       <c r="B4" s="24"/>
       <c r="C4" s="22" t="s">
@@ -1943,7 +1648,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="43.5" customHeight="1">
+    <row r="5" ht="43.5" customHeight="1" spans="1:4">
       <c r="A5" s="20"/>
       <c r="B5" s="24"/>
       <c r="C5" s="22" t="s">
@@ -1953,7 +1658,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="43.5" customHeight="1">
+    <row r="6" ht="43.5" customHeight="1" spans="1:4">
       <c r="A6" s="20"/>
       <c r="B6" s="21" t="s">
         <v>13</v>
@@ -1965,10 +1670,10 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="43.5" customHeight="1">
+    <row r="7" ht="43.5" customHeight="1" spans="1:4">
       <c r="A7" s="20"/>
       <c r="B7" s="24"/>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="26" t="s">
         <v>16</v>
       </c>
       <c r="D7" s="23" t="s">
@@ -1983,33 +1688,35 @@
     <mergeCell ref="B6:B7"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="C3" location="'网络运维服务（040201）'!A1" display="网络运维服务_x000a_（040201）"/>
-    <hyperlink ref="C4" location="'主机运维服务（040202)'!A1" display="主机运维服务_x000a_（040202）"/>
-    <hyperlink ref="C5" location="'其他硬件运维服务 （040299）'!A1" display="其他硬件运维服务_x000a_（040299）"/>
-    <hyperlink ref="C6" location="'基础软件运维服务 （040301）'!A1" display="基础软件运维服务_x000a_（040301）"/>
-    <hyperlink ref="C7" location="'应用软件运维服务 （040303）'!A1" display="应用软件运维服务_x000a_（040303）"/>
+    <hyperlink ref="C3" location="'网络运维服务（040201）'!A1" display="网络运维服务&#10;（040201）"/>
+    <hyperlink ref="C4" location="'主机运维服务（040202)'!A1" display="主机运维服务&#10;（040202）"/>
+    <hyperlink ref="C5" location="'其他硬件运维服务 （040299）'!A1" display="其他硬件运维服务&#10;（040299）"/>
+    <hyperlink ref="C6" location="'基础软件运维服务 （040301）'!A1" display="基础软件运维服务&#10;（040301）"/>
+    <hyperlink ref="C7" location="'应用软件运维服务 （040303）'!A1" display="应用软件运维服务&#10;（040303）"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="23.875" customWidth="1"/>
     <col min="2" max="2" width="104.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="19.9" customHeight="1">
+    <row r="1" ht="19.9" customHeight="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:2" ht="15.75" customHeight="1">
+    <row r="2" ht="15.75" customHeight="1" spans="1:2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -2017,7 +1724,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="18.75" customHeight="1">
+    <row r="3" ht="18.75" customHeight="1" spans="1:2">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -2027,7 +1734,7 @@
 （0402）</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="18.75" customHeight="1">
+    <row r="4" ht="18.75" customHeight="1" spans="1:2">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -2035,15 +1742,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="18.75" customHeight="1">
+    <row r="5" ht="18.75" customHeight="1" spans="1:2">
       <c r="A5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="27" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="18.75" customHeight="1">
+    <row r="6" ht="18.75" customHeight="1" spans="1:2">
       <c r="A6" s="2" t="s">
         <v>22</v>
       </c>
@@ -2051,7 +1758,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="18.75" customHeight="1">
+    <row r="7" ht="18.75" customHeight="1" spans="1:2">
       <c r="A7" s="2" t="s">
         <v>24</v>
       </c>
@@ -2059,13 +1766,13 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="18.75" customHeight="1">
+    <row r="8" ht="18.75" customHeight="1" spans="1:2">
       <c r="A8" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B8" s="2"/>
     </row>
-    <row r="9" spans="1:2" ht="18.75" customHeight="1">
+    <row r="9" ht="18.75" customHeight="1" spans="1:2">
       <c r="A9" s="2" t="s">
         <v>27</v>
       </c>
@@ -2073,7 +1780,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="18.75" customHeight="1">
+    <row r="10" ht="18.75" customHeight="1" spans="1:2">
       <c r="A10" s="5" t="s">
         <v>29</v>
       </c>
@@ -2081,43 +1788,43 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="18.75" customHeight="1">
+    <row r="11" ht="18.75" customHeight="1" spans="1:2">
       <c r="A11" s="6"/>
       <c r="B11" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="18.75" customHeight="1">
+    <row r="12" ht="18.75" customHeight="1" spans="1:2">
       <c r="A12" s="6"/>
       <c r="B12" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="18.75" customHeight="1">
+    <row r="13" ht="18.75" customHeight="1" spans="1:2">
       <c r="A13" s="6"/>
       <c r="B13" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="18.75" customHeight="1">
+    <row r="14" ht="18.75" customHeight="1" spans="1:2">
       <c r="A14" s="6"/>
       <c r="B14" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="18.75" customHeight="1">
+    <row r="15" ht="18.75" customHeight="1" spans="1:2">
       <c r="A15" s="6"/>
       <c r="B15" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="18.75" customHeight="1">
+    <row r="16" ht="18.75" customHeight="1" spans="1:2">
       <c r="A16" s="7"/>
       <c r="B16" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="18.75" customHeight="1">
+    <row r="17" ht="18.75" customHeight="1" spans="1:2">
       <c r="A17" s="2" t="s">
         <v>37</v>
       </c>
@@ -2125,7 +1832,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="18.75" customHeight="1">
+    <row r="18" ht="18.75" customHeight="1" spans="1:2">
       <c r="A18" s="5" t="s">
         <v>39</v>
       </c>
@@ -2133,31 +1840,31 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="18.75" customHeight="1">
+    <row r="19" ht="18.75" customHeight="1" spans="1:2">
       <c r="A19" s="6"/>
       <c r="B19" s="8" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="18.75" customHeight="1">
+    <row r="20" ht="18.75" customHeight="1" spans="1:2">
       <c r="A20" s="6"/>
       <c r="B20" s="8" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="18.75" customHeight="1">
+    <row r="21" ht="18.75" customHeight="1" spans="1:2">
       <c r="A21" s="6"/>
       <c r="B21" s="8" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="18.75" customHeight="1">
+    <row r="22" ht="18.75" customHeight="1" spans="1:2">
       <c r="A22" s="7"/>
       <c r="B22" s="8" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="18.75" customHeight="1">
+    <row r="23" ht="18.75" customHeight="1" spans="1:2">
       <c r="A23" s="2" t="s">
         <v>45</v>
       </c>
@@ -2165,7 +1872,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="18.75" customHeight="1">
+    <row r="24" ht="18.75" customHeight="1" spans="1:2">
       <c r="A24" s="2" t="s">
         <v>47</v>
       </c>
@@ -2173,7 +1880,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="18.75" customHeight="1">
+    <row r="25" ht="18.75" customHeight="1" spans="1:2">
       <c r="A25" s="2" t="s">
         <v>49</v>
       </c>
@@ -2181,7 +1888,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="18.75" customHeight="1">
+    <row r="26" ht="18.75" customHeight="1" spans="1:2">
       <c r="A26" s="2" t="s">
         <v>51</v>
       </c>
@@ -2198,26 +1905,28 @@
   </mergeCells>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="24.5" customWidth="1"/>
     <col min="2" max="2" width="102.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1">
+    <row r="1" ht="18.75" customHeight="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>53</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:2" ht="16.5" customHeight="1">
+    <row r="2" ht="16.5" customHeight="1" spans="1:2">
       <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
@@ -2225,7 +1934,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="16.5" customHeight="1">
+    <row r="3" ht="16.5" customHeight="1" spans="1:2">
       <c r="A3" s="10" t="s">
         <v>2</v>
       </c>
@@ -2235,7 +1944,7 @@
 （0402）</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="16.5" customHeight="1">
+    <row r="4" ht="16.5" customHeight="1" spans="1:2">
       <c r="A4" s="10" t="s">
         <v>3</v>
       </c>
@@ -2243,15 +1952,15 @@
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="16.5" customHeight="1">
+    <row r="5" ht="16.5" customHeight="1" spans="1:2">
       <c r="A5" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="28" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="16.5" customHeight="1">
+    <row r="6" ht="16.5" customHeight="1" spans="1:2">
       <c r="A6" s="10" t="s">
         <v>22</v>
       </c>
@@ -2259,7 +1968,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="16.5" customHeight="1">
+    <row r="7" ht="16.5" customHeight="1" spans="1:2">
       <c r="A7" s="10" t="s">
         <v>24</v>
       </c>
@@ -2267,13 +1976,13 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="16.5" customHeight="1">
+    <row r="8" ht="16.5" customHeight="1" spans="1:2">
       <c r="A8" s="12" t="s">
         <v>26</v>
       </c>
       <c r="B8" s="13"/>
     </row>
-    <row r="9" spans="1:2" ht="16.5" customHeight="1">
+    <row r="9" ht="16.5" customHeight="1" spans="1:2">
       <c r="A9" s="10" t="s">
         <v>27</v>
       </c>
@@ -2281,7 +1990,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="16.5" customHeight="1">
+    <row r="10" ht="16.5" customHeight="1" spans="1:2">
       <c r="A10" s="5" t="s">
         <v>29</v>
       </c>
@@ -2289,61 +1998,61 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="16.5" customHeight="1">
+    <row r="11" ht="16.5" customHeight="1" spans="1:2">
       <c r="A11" s="6"/>
       <c r="B11" s="11" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="16.5" customHeight="1">
+    <row r="12" ht="16.5" customHeight="1" spans="1:2">
       <c r="A12" s="6"/>
       <c r="B12" s="11" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="16.5" customHeight="1">
+    <row r="13" ht="16.5" customHeight="1" spans="1:2">
       <c r="A13" s="6"/>
       <c r="B13" s="11" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="16.5" customHeight="1">
+    <row r="14" ht="16.5" customHeight="1" spans="1:2">
       <c r="A14" s="6"/>
       <c r="B14" s="11" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="16.5" customHeight="1">
+    <row r="15" ht="16.5" customHeight="1" spans="1:2">
       <c r="A15" s="6"/>
       <c r="B15" s="11" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="16.5" customHeight="1">
+    <row r="16" ht="16.5" customHeight="1" spans="1:2">
       <c r="A16" s="6"/>
       <c r="B16" s="11" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="16.5" customHeight="1">
+    <row r="17" ht="16.5" customHeight="1" spans="1:2">
       <c r="A17" s="6"/>
       <c r="B17" s="11" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="16.5" customHeight="1">
+    <row r="18" ht="16.5" customHeight="1" spans="1:2">
       <c r="A18" s="6"/>
       <c r="B18" s="14" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="16.5" customHeight="1">
+    <row r="19" ht="16.5" customHeight="1" spans="1:2">
       <c r="A19" s="7"/>
       <c r="B19" s="15" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="16.5" customHeight="1">
+    <row r="20" ht="16.5" customHeight="1" spans="1:2">
       <c r="A20" s="10" t="s">
         <v>37</v>
       </c>
@@ -2351,7 +2060,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="16.5" customHeight="1">
+    <row r="21" ht="16.5" customHeight="1" spans="1:2">
       <c r="A21" s="5" t="s">
         <v>39</v>
       </c>
@@ -2359,31 +2068,31 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="16.5" customHeight="1">
+    <row r="22" ht="16.5" customHeight="1" spans="1:2">
       <c r="A22" s="6"/>
       <c r="B22" s="8" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="16.5" customHeight="1">
+    <row r="23" ht="16.5" customHeight="1" spans="1:2">
       <c r="A23" s="6"/>
       <c r="B23" s="8" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="16.5" customHeight="1">
+    <row r="24" ht="16.5" customHeight="1" spans="1:2">
       <c r="A24" s="6"/>
       <c r="B24" s="8" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="16.5" customHeight="1">
+    <row r="25" ht="16.5" customHeight="1" spans="1:2">
       <c r="A25" s="7"/>
       <c r="B25" s="8" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="16.5" customHeight="1">
+    <row r="26" ht="16.5" customHeight="1" spans="1:2">
       <c r="A26" s="10" t="s">
         <v>45</v>
       </c>
@@ -2391,7 +2100,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="16.5" customHeight="1">
+    <row r="27" ht="16.5" customHeight="1" spans="1:2">
       <c r="A27" s="10" t="s">
         <v>47</v>
       </c>
@@ -2399,7 +2108,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="16.5" customHeight="1">
+    <row r="28" ht="16.5" customHeight="1" spans="1:2">
       <c r="A28" s="10" t="s">
         <v>49</v>
       </c>
@@ -2407,7 +2116,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="16.5" customHeight="1">
+    <row r="29" ht="16.5" customHeight="1" spans="1:2">
       <c r="A29" s="10" t="s">
         <v>51</v>
       </c>
@@ -2423,26 +2132,28 @@
     <mergeCell ref="A21:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="25.625" customWidth="1"/>
     <col min="2" max="2" width="102.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="23.65" customHeight="1">
+    <row r="1" ht="23.65" customHeight="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>70</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:2" ht="18.75" customHeight="1">
+    <row r="2" ht="18.75" customHeight="1" spans="1:2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -2450,7 +2161,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="18.75" customHeight="1">
+    <row r="3" ht="18.75" customHeight="1" spans="1:2">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -2460,7 +2171,7 @@
 （0402）</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="18.75" customHeight="1">
+    <row r="4" ht="18.75" customHeight="1" spans="1:2">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -2468,15 +2179,15 @@
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="18.75" customHeight="1">
+    <row r="5" ht="18.75" customHeight="1" spans="1:2">
       <c r="A5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="27" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="28.15" customHeight="1">
+    <row r="6" ht="28.15" customHeight="1" spans="1:2">
       <c r="A6" s="2" t="s">
         <v>22</v>
       </c>
@@ -2484,7 +2195,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="18.75" customHeight="1">
+    <row r="7" ht="18.75" customHeight="1" spans="1:2">
       <c r="A7" s="2" t="s">
         <v>24</v>
       </c>
@@ -2492,13 +2203,13 @@
         <v>74</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="18.75" customHeight="1">
+    <row r="8" ht="18.75" customHeight="1" spans="1:2">
       <c r="A8" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B8" s="2"/>
     </row>
-    <row r="9" spans="1:2" ht="36.4" customHeight="1">
+    <row r="9" ht="36.4" customHeight="1" spans="1:2">
       <c r="A9" s="2" t="s">
         <v>27</v>
       </c>
@@ -2506,7 +2217,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="18.75" customHeight="1">
+    <row r="10" ht="18.75" customHeight="1" spans="1:2">
       <c r="A10" s="5" t="s">
         <v>29</v>
       </c>
@@ -2514,31 +2225,31 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="18.75" customHeight="1">
+    <row r="11" ht="18.75" customHeight="1" spans="1:2">
       <c r="A11" s="6"/>
       <c r="B11" s="3" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="18.75" customHeight="1">
+    <row r="12" ht="18.75" customHeight="1" spans="1:2">
       <c r="A12" s="6"/>
       <c r="B12" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="18.75" customHeight="1">
+    <row r="13" ht="18.75" customHeight="1" spans="1:2">
       <c r="A13" s="6"/>
       <c r="B13" s="3" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="18.75" customHeight="1">
+    <row r="14" ht="18.75" customHeight="1" spans="1:2">
       <c r="A14" s="6"/>
       <c r="B14" s="3" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="18.75" customHeight="1">
+    <row r="15" ht="18.75" customHeight="1" spans="1:2">
       <c r="A15" s="2" t="s">
         <v>37</v>
       </c>
@@ -2546,7 +2257,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="18.75" customHeight="1">
+    <row r="16" ht="18.75" customHeight="1" spans="1:2">
       <c r="A16" s="5" t="s">
         <v>39</v>
       </c>
@@ -2554,31 +2265,31 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="18.75" customHeight="1">
+    <row r="17" ht="18.75" customHeight="1" spans="1:2">
       <c r="A17" s="6"/>
       <c r="B17" s="8" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="18.75" customHeight="1">
+    <row r="18" ht="18.75" customHeight="1" spans="1:2">
       <c r="A18" s="6"/>
       <c r="B18" s="8" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="18.75" customHeight="1">
+    <row r="19" ht="18.75" customHeight="1" spans="1:2">
       <c r="A19" s="6"/>
       <c r="B19" s="8" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="18.75" customHeight="1">
+    <row r="20" ht="18.75" customHeight="1" spans="1:2">
       <c r="A20" s="7"/>
       <c r="B20" s="8" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="18.75" customHeight="1">
+    <row r="21" ht="18.75" customHeight="1" spans="1:2">
       <c r="A21" s="2" t="s">
         <v>45</v>
       </c>
@@ -2586,7 +2297,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="18.75" customHeight="1">
+    <row r="22" ht="18.75" customHeight="1" spans="1:2">
       <c r="A22" s="2" t="s">
         <v>47</v>
       </c>
@@ -2594,7 +2305,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="18.75" customHeight="1">
+    <row r="23" ht="18.75" customHeight="1" spans="1:2">
       <c r="A23" s="2" t="s">
         <v>49</v>
       </c>
@@ -2602,7 +2313,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="18.75" customHeight="1">
+    <row r="24" ht="18.75" customHeight="1" spans="1:2">
       <c r="A24" s="2" t="s">
         <v>51</v>
       </c>
@@ -2618,26 +2329,28 @@
     <mergeCell ref="A16:A20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="22.75" customWidth="1"/>
     <col min="2" max="2" width="105.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="21.75" customHeight="1">
+    <row r="1" ht="21.75" customHeight="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:2" ht="18" customHeight="1">
+    <row r="2" ht="18" customHeight="1" spans="1:2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -2645,7 +2358,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="18" customHeight="1">
+    <row r="3" ht="18" customHeight="1" spans="1:2">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -2655,7 +2368,7 @@
 （0403）</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="18" customHeight="1">
+    <row r="4" ht="18" customHeight="1" spans="1:2">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -2663,15 +2376,15 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="18" customHeight="1">
+    <row r="5" ht="18" customHeight="1" spans="1:2">
       <c r="A5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="27" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="28.8">
+    <row r="6" ht="27" spans="1:2">
       <c r="A6" s="2" t="s">
         <v>22</v>
       </c>
@@ -2679,7 +2392,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="21" customHeight="1">
+    <row r="7" ht="21" customHeight="1" spans="1:2">
       <c r="A7" s="2" t="s">
         <v>24</v>
       </c>
@@ -2687,13 +2400,13 @@
         <v>86</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="18" customHeight="1">
+    <row r="8" ht="18" customHeight="1" spans="1:2">
       <c r="A8" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B8" s="2"/>
     </row>
-    <row r="9" spans="1:2" ht="18" customHeight="1">
+    <row r="9" ht="18" customHeight="1" spans="1:2">
       <c r="A9" s="2" t="s">
         <v>27</v>
       </c>
@@ -2701,7 +2414,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="18" customHeight="1">
+    <row r="10" ht="18" customHeight="1" spans="1:2">
       <c r="A10" s="5" t="s">
         <v>29</v>
       </c>
@@ -2709,43 +2422,43 @@
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="18" customHeight="1">
+    <row r="11" ht="18" customHeight="1" spans="1:2">
       <c r="A11" s="6"/>
       <c r="B11" s="3" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="18" customHeight="1">
+    <row r="12" ht="18" customHeight="1" spans="1:2">
       <c r="A12" s="6"/>
       <c r="B12" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="18" customHeight="1">
+    <row r="13" ht="18" customHeight="1" spans="1:2">
       <c r="A13" s="6"/>
       <c r="B13" s="3" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="18" customHeight="1">
+    <row r="14" ht="18" customHeight="1" spans="1:2">
       <c r="A14" s="6"/>
       <c r="B14" s="3" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="18" customHeight="1">
+    <row r="15" ht="18" customHeight="1" spans="1:2">
       <c r="A15" s="6"/>
       <c r="B15" s="3" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="18" customHeight="1">
+    <row r="16" ht="18" customHeight="1" spans="1:2">
       <c r="A16" s="7"/>
       <c r="B16" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="18" customHeight="1">
+    <row r="17" ht="18" customHeight="1" spans="1:2">
       <c r="A17" s="2" t="s">
         <v>37</v>
       </c>
@@ -2753,7 +2466,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="18" customHeight="1">
+    <row r="18" ht="18" customHeight="1" spans="1:2">
       <c r="A18" s="5" t="s">
         <v>39</v>
       </c>
@@ -2761,31 +2474,31 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="18" customHeight="1">
+    <row r="19" ht="18" customHeight="1" spans="1:2">
       <c r="A19" s="6"/>
       <c r="B19" s="8" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="18" customHeight="1">
+    <row r="20" ht="18" customHeight="1" spans="1:2">
       <c r="A20" s="6"/>
       <c r="B20" s="8" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="18" customHeight="1">
+    <row r="21" ht="18" customHeight="1" spans="1:2">
       <c r="A21" s="6"/>
       <c r="B21" s="8" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="18" customHeight="1">
+    <row r="22" ht="18" customHeight="1" spans="1:2">
       <c r="A22" s="7"/>
       <c r="B22" s="8" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="18" customHeight="1">
+    <row r="23" ht="18" customHeight="1" spans="1:2">
       <c r="A23" s="2" t="s">
         <v>45</v>
       </c>
@@ -2793,7 +2506,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="18" customHeight="1">
+    <row r="24" ht="18" customHeight="1" spans="1:2">
       <c r="A24" s="2" t="s">
         <v>47</v>
       </c>
@@ -2801,7 +2514,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="18" customHeight="1">
+    <row r="25" ht="18" customHeight="1" spans="1:2">
       <c r="A25" s="2" t="s">
         <v>49</v>
       </c>
@@ -2809,7 +2522,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="18" customHeight="1">
+    <row r="26" ht="18" customHeight="1" spans="1:2">
       <c r="A26" s="2" t="s">
         <v>51</v>
       </c>
@@ -2825,26 +2538,28 @@
     <mergeCell ref="A18:A22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="23.125" customWidth="1"/>
     <col min="2" max="2" width="105.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="21" customHeight="1">
+    <row r="1" ht="21" customHeight="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>95</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:2" ht="17.25" customHeight="1">
+    <row r="2" ht="17.25" customHeight="1" spans="1:2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -2852,7 +2567,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="17.25" customHeight="1">
+    <row r="3" ht="17.25" customHeight="1" spans="1:2">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -2862,7 +2577,7 @@
 （0403）</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="17.25" customHeight="1">
+    <row r="4" ht="17.25" customHeight="1" spans="1:2">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -2870,15 +2585,15 @@
         <v>96</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="17.25" customHeight="1">
+    <row r="5" ht="17.25" customHeight="1" spans="1:2">
       <c r="A5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="27" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="28.8">
+    <row r="6" ht="27" spans="1:2">
       <c r="A6" s="2" t="s">
         <v>22</v>
       </c>
@@ -2886,7 +2601,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="21" customHeight="1">
+    <row r="7" ht="21" customHeight="1" spans="1:2">
       <c r="A7" s="2" t="s">
         <v>24</v>
       </c>
@@ -2894,13 +2609,13 @@
         <v>99</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="21" customHeight="1">
+    <row r="8" ht="21" customHeight="1" spans="1:2">
       <c r="A8" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B8" s="2"/>
     </row>
-    <row r="9" spans="1:2" ht="14.4">
+    <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
         <v>27</v>
       </c>
@@ -2908,7 +2623,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="17.25" customHeight="1">
+    <row r="10" ht="17.25" customHeight="1" spans="1:2">
       <c r="A10" s="5" t="s">
         <v>29</v>
       </c>
@@ -2916,43 +2631,43 @@
         <v>101</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="17.25" customHeight="1">
+    <row r="11" ht="17.25" customHeight="1" spans="1:2">
       <c r="A11" s="6"/>
       <c r="B11" s="3" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="17.25" customHeight="1">
+    <row r="12" ht="17.25" customHeight="1" spans="1:2">
       <c r="A12" s="6"/>
       <c r="B12" s="3" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="17.25" customHeight="1">
+    <row r="13" ht="17.25" customHeight="1" spans="1:2">
       <c r="A13" s="6"/>
       <c r="B13" s="3" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="17.25" customHeight="1">
+    <row r="14" ht="17.25" customHeight="1" spans="1:2">
       <c r="A14" s="6"/>
       <c r="B14" s="3" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="30" customHeight="1">
+    <row r="15" ht="30" customHeight="1" spans="1:2">
       <c r="A15" s="6"/>
       <c r="B15" s="4" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="17.25" customHeight="1">
+    <row r="16" ht="17.25" customHeight="1" spans="1:2">
       <c r="A16" s="7"/>
       <c r="B16" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="17.25" customHeight="1">
+    <row r="17" ht="17.25" customHeight="1" spans="1:2">
       <c r="A17" s="2" t="s">
         <v>37</v>
       </c>
@@ -2960,7 +2675,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="17.25" customHeight="1">
+    <row r="18" ht="17.25" customHeight="1" spans="1:2">
       <c r="A18" s="5" t="s">
         <v>39</v>
       </c>
@@ -2968,31 +2683,31 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="17.25" customHeight="1">
+    <row r="19" ht="17.25" customHeight="1" spans="1:2">
       <c r="A19" s="6"/>
       <c r="B19" s="8" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="17.25" customHeight="1">
+    <row r="20" ht="17.25" customHeight="1" spans="1:2">
       <c r="A20" s="6"/>
       <c r="B20" s="8" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="17.25" customHeight="1">
+    <row r="21" ht="17.25" customHeight="1" spans="1:2">
       <c r="A21" s="6"/>
       <c r="B21" s="8" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="17.25" customHeight="1">
+    <row r="22" ht="17.25" customHeight="1" spans="1:2">
       <c r="A22" s="7"/>
       <c r="B22" s="8" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="17.25" customHeight="1">
+    <row r="23" ht="17.25" customHeight="1" spans="1:2">
       <c r="A23" s="2" t="s">
         <v>45</v>
       </c>
@@ -3000,7 +2715,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="17.25" customHeight="1">
+    <row r="24" ht="17.25" customHeight="1" spans="1:2">
       <c r="A24" s="2" t="s">
         <v>47</v>
       </c>
@@ -3008,7 +2723,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="17.25" customHeight="1">
+    <row r="25" ht="17.25" customHeight="1" spans="1:2">
       <c r="A25" s="2" t="s">
         <v>49</v>
       </c>
@@ -3016,7 +2731,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="17.25" customHeight="1">
+    <row r="26" ht="17.25" customHeight="1" spans="1:2">
       <c r="A26" s="2" t="s">
         <v>51</v>
       </c>
@@ -3032,6 +2747,7 @@
     <mergeCell ref="A18:A22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/1-运维服务目录/0102-组织级运维服务目录.xlsx
+++ b/1-运维服务目录/0102-组织级运维服务目录.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="18180" tabRatio="954" activeTab="3"/>
+    <workbookView windowHeight="18180" tabRatio="954" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="服务目录" sheetId="8" r:id="rId1"/>
@@ -410,28 +410,28 @@
     <t>040299</t>
   </si>
   <si>
-    <t xml:space="preserve">LED 显示与液晶拼接屏，数据传输终端DTU， PLC可编程逻辑控制器、物联网多功能电表、物联网多功能水表、物联网电子称、电表集中器、中控设备、空调等设备进行的例行检查及状态监控、响应支持、故障处理、性能优化等服务 </t>
+    <t>PS软件系统运行相关的硬件设备，提供例行检查、状态监控、故障处理、性能优化等服务，保障软件系统正常运行所需的硬件环境</t>
   </si>
   <si>
     <t xml:space="preserve">保障和提升相关硬件的可用性 </t>
   </si>
   <si>
-    <t>LED 显示与液晶拼接屏，数据传输终端DTU， PLC可编程逻辑控制器、物联网多功能电表、物联网多功能水表、物联网电子称、电表集中器、中控设备、空调等</t>
-  </si>
-  <si>
-    <t>1、各种信息点位的巡检维护；</t>
-  </si>
-  <si>
-    <t>2、采集、监控系统前端设备及后端设备的维护；</t>
-  </si>
-  <si>
-    <t>3、检测报警系统的维护；</t>
-  </si>
-  <si>
-    <t>4、采集、监控系统的维护；</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5、按客户内部工作规范和流程的要求，完成客户领导交办的其它相关工作。 </t>
+    <t>日常业务中与畅捷通软件系统运行相关的硬件设备，包括：计算机终端、服务器、打印机、网络设备及其他外设</t>
+  </si>
+  <si>
+    <t>1、硬件设备日常巡检与状态检查</t>
+  </si>
+  <si>
+    <t>2、硬件故障诊断与现场/远程处理</t>
+  </si>
+  <si>
+    <t>3、硬件性能监控与优化建议</t>
+  </si>
+  <si>
+    <t>4、打印机、扫描仪等外设的驱动安装与调试</t>
+  </si>
+  <si>
+    <t>5、硬件更换时的安装与配置支持</t>
   </si>
   <si>
     <t>巡检：每天1次/每周1次或双方协定</t>

--- a/1-运维服务目录/0102-组织级运维服务目录.xlsx
+++ b/1-运维服务目录/0102-组织级运维服务目录.xlsx
@@ -75,23 +75,34 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>面向LED 显示与液晶拼接屏，数据传输终端DTU， PLC可编程逻辑控制器、物联网多功能电表、物联网多功能水表、物联网电子称、电表集中器、中控设备、空调等其他硬件设备的运维服务</t>
+      <t>面向</t>
     </r>
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF000000"/>
+        <color rgb="FF0F1115"/>
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>。</t>
+      <t>畅捷通</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>SPS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>产品运行所依赖的硬件设备，提供例行检查、状态监控、故障处理、性能优化等服务，保障软件系统正常运行所需的硬件环境安全与稳定</t>
     </r>
   </si>
   <si>
@@ -110,7 +121,7 @@
 （040303）</t>
   </si>
   <si>
-    <t>面向生态环境云平台、噪声污染监测系统、水质在线检测系统、空气质量检测系统等应用软件的运维服务。</t>
+    <t>面向畅捷通SPS产品，提供全方位的应用软件运维服务，包括系统健康检查、数据备份、软件更新、故障处理、用户权限管理及知识转移服务，保障业务系统稳定运行和客户团队能力提升</t>
   </si>
   <si>
     <t>网络运维服务（040201）</t>
@@ -410,10 +421,10 @@
     <t>040299</t>
   </si>
   <si>
-    <t>PS软件系统运行相关的硬件设备，提供例行检查、状态监控、故障处理、性能优化等服务，保障软件系统正常运行所需的硬件环境</t>
-  </si>
-  <si>
-    <t xml:space="preserve">保障和提升相关硬件的可用性 </t>
+    <t>面向畅捷通SPS产品运行所依赖的硬件设备，提供例行检查、状态监控、故障处理、性能优化等服务，保障软件系统正常运行所需的硬件环境安全与稳定</t>
+  </si>
+  <si>
+    <t>保障SPS产品运行所需硬件环境的可用性与安全性</t>
   </si>
   <si>
     <t>日常业务中与畅捷通软件系统运行相关的硬件设备，包括：计算机终端、服务器、打印机、网络设备及其他外设</t>
@@ -446,7 +457,7 @@
     <t>040301</t>
   </si>
   <si>
-    <t xml:space="preserve">定期在现场对基础软件各项参数和指标进行全面检查；在现场为客户 提供定期备份各项数据；清理冗余数据；及时发现故障隐患，对已经发现 的问题进行修复，保证客户的软件运行正常。 </t>
+    <t xml:space="preserve"> 定期对基础软件各项参数和指标进行全面检查，提供数据备份、冗余清理、故障排查等服务，确保SPS产品运行的基础软件环境稳定可靠</t>
   </si>
   <si>
     <t xml:space="preserve">确保操作系统运行正常，对客户的申报及发现隐患进行改进。 </t>
@@ -528,7 +539,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -703,6 +714,18 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF0F1115"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
   </fonts>
